--- a/examples/financials_poisoned.xlsx
+++ b/examples/financials_poisoned.xlsx
@@ -21,8 +21,8 @@
     <numFmt numFmtId="165" formatCode="&quot;$98,200,000&quot;"/>
     <numFmt numFmtId="166" formatCode="&quot;$29,200,000&quot;"/>
     <numFmt numFmtId="167" formatCode="&quot;22.9%&quot;"/>
-    <numFmt numFmtId="168" formatCode="&quot;$18,900,000&quot;"/>
-    <numFmt numFmtId="169" formatCode="&quot;$8,400,000&quot;"/>
+    <numFmt numFmtId="168" formatCode="&quot;$15,800,000&quot;"/>
+    <numFmt numFmtId="169" formatCode="&quot;$7,200,000&quot;"/>
     <numFmt numFmtId="170" formatCode="&quot;$6,200,000&quot;"/>
     <numFmt numFmtId="171" formatCode="&quot;4.9%&quot;"/>
     <numFmt numFmtId="172" formatCode="&quot;$4,100,000&quot;"/>
@@ -744,7 +744,7 @@
         </is>
       </c>
       <c r="B17" s="13" t="n">
-        <v>20100000</v>
+        <v>16500000</v>
       </c>
     </row>
     <row r="18">
@@ -754,7 +754,7 @@
         </is>
       </c>
       <c r="B18" s="14" t="n">
-        <v>9200000</v>
+        <v>8600000</v>
       </c>
     </row>
     <row r="19">
